--- a/untranslated/downloads/data-excel/15.1.1.1.xlsx
+++ b/untranslated/downloads/data-excel/15.1.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B382AA0F-056B-4EA4-A05C-D7439CDDC87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -15,14 +16,6 @@
     <definedName name="Button_2">"Pokreal_CHC_List"</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -202,18 +195,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_р_._-;\-* #,##0.00_р_._-;_-* &quot;-&quot;??_р_._-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _р_._-;\-* #,##0.00\ _р_._-;_-* &quot;-&quot;??\ _р_._-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -401,132 +402,141 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="23">
+  <cellStyleXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="23">
-    <cellStyle name="Normal 17" xfId="19"/>
-    <cellStyle name="Normal 2" xfId="21"/>
+  <cellStyles count="27">
+    <cellStyle name="Normal 17" xfId="19" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="24" xr:uid="{BB78F853-3ACB-4336-8BF0-5F0B5AA16234}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 10" xfId="3"/>
-    <cellStyle name="Обычный 11" xfId="22"/>
-    <cellStyle name="Обычный 2" xfId="4"/>
-    <cellStyle name="Обычный 2 2" xfId="5"/>
-    <cellStyle name="Обычный 2 3" xfId="6"/>
-    <cellStyle name="Обычный 3" xfId="7"/>
-    <cellStyle name="Обычный 3 2" xfId="8"/>
-    <cellStyle name="Обычный 4" xfId="9"/>
-    <cellStyle name="Обычный 5" xfId="10"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="1"/>
-    <cellStyle name="Обычный 7 2" xfId="20"/>
-    <cellStyle name="Обычный 8" xfId="11"/>
-    <cellStyle name="Обычный 9" xfId="12"/>
-    <cellStyle name="Пояснение 2" xfId="13"/>
-    <cellStyle name="Процентный 2" xfId="14"/>
-    <cellStyle name="Процентный 3" xfId="15"/>
-    <cellStyle name="Стиль 1" xfId="16"/>
-    <cellStyle name="Финансовый 2" xfId="17"/>
-    <cellStyle name="Финансовый 3" xfId="18"/>
+    <cellStyle name="Обычный 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 11" xfId="22" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 11 2" xfId="25" xr:uid="{EA82EA53-BD28-4E3D-ABB2-7026AA4DFB95}"/>
+    <cellStyle name="Обычный 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 3 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 4" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 5" xfId="10" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 7" xfId="1" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 7 2" xfId="20" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 7 3" xfId="26" xr:uid="{A244A1EC-77E7-4F4F-9480-B62E8CE6D32B}"/>
+    <cellStyle name="Обычный 7 4" xfId="23" xr:uid="{1D49F2E8-B1D3-429D-8EFF-551DBFA66237}"/>
+    <cellStyle name="Обычный 8" xfId="11" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Обычный 9" xfId="12" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Пояснение 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Процентный 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Процентный 3" xfId="15" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Стиль 1" xfId="16" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Финансовый 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Финансовый 3" xfId="18" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -542,9 +552,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -582,9 +592,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -619,7 +629,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -654,7 +664,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -827,15 +837,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="33.85546875" customWidth="1"/>
     <col min="4" max="15" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="42.75" customHeight="1">
+    <row r="1" spans="1:16" ht="42.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -857,7 +867,7 @@
       <c r="M1" s="16"/>
       <c r="N1" s="16"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
@@ -879,7 +889,7 @@
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="1:15" ht="15.75" thickBot="1">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -895,7 +905,7 @@
       <c r="M3" s="16"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1">
+    <row r="4" spans="1:16" ht="15.75" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -935,14 +945,17 @@
       <c r="M4" s="17">
         <v>2021</v>
       </c>
-      <c r="N4" s="23" t="s">
+      <c r="N4" s="22" t="s">
         <v>35</v>
       </c>
       <c r="O4" s="17">
         <v>2023</v>
       </c>
+      <c r="P4" s="24">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1001,11 @@
       <c r="O5" s="18">
         <v>6.3</v>
       </c>
+      <c r="P5" s="25">
+        <v>6.4</v>
+      </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1035,8 +1051,11 @@
       <c r="O6" s="19">
         <v>0.8</v>
       </c>
+      <c r="P6" s="26">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -1082,8 +1101,11 @@
       <c r="O7" s="19">
         <v>2.4</v>
       </c>
+      <c r="P7" s="26">
+        <v>2.4</v>
+      </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
@@ -1129,8 +1151,11 @@
       <c r="O8" s="19">
         <v>0.7</v>
       </c>
+      <c r="P8" s="26">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1176,8 +1201,11 @@
       <c r="O9" s="19">
         <v>0.8</v>
       </c>
+      <c r="P9" s="26">
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1223,8 +1251,11 @@
       <c r="O10" s="19">
         <v>1</v>
       </c>
+      <c r="P10" s="26">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
@@ -1270,8 +1301,11 @@
       <c r="O11" s="19">
         <v>0.2</v>
       </c>
+      <c r="P11" s="26">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" thickBot="1">
+    <row r="12" spans="1:16" ht="15.75" thickBot="1">
       <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
@@ -1317,15 +1351,18 @@
       <c r="O12" s="20">
         <v>0.4</v>
       </c>
+      <c r="P12" s="27">
+        <v>0.4</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" ht="33.75">
+    <row r="13" spans="1:16" ht="33.75">
       <c r="A13" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D13" s="16"/>
@@ -1340,14 +1377,14 @@
       <c r="M13" s="16"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:15" ht="45">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:16" ht="45">
+      <c r="A14" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="23" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="16"/>
